--- a/artfynd/A 55498-2025 artfynd.xlsx
+++ b/artfynd/A 55498-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000427</v>
+        <v>88571415</v>
       </c>
       <c r="B2" t="n">
-        <v>78801</v>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hue</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nylandet, Hls</t>
+          <t>Norr-Ensjön, Riberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526749</v>
+        <v>526755</v>
       </c>
       <c r="R2" t="n">
-        <v>6909043</v>
+        <v>6909000</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,15 +760,1027 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>87749285</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>526322</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6908579</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>87748226</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>526323</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6908580</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>87748233</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>526737</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6908624</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129000427</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nylandet, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>526749</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6909043</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>87747842</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>526300</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6908985</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>87747840</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>526365</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6908938</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>87748056</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>526440</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6908530</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>87748057</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>526473</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6908515</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>86451789</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Blåtjärnen, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>526760</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6908608</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-06-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tim Hipkiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>87748227</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Riberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>526737</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6908624</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-07-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55498-2025 artfynd.xlsx
+++ b/artfynd/A 55498-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88571415</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87749285</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748226</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748233</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000427</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87747842</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87747840</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748056</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1582,6 +1627,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748057</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1684,6 +1734,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86451789</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,8 +1836,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87748227</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>